--- a/artfynd/A 7337-2025 artfynd.xlsx
+++ b/artfynd/A 7337-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,117 +1602,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>121172387</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bickberg, Vrm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>386869</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6653009</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På liggande björk.</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Jan Hedin</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Jan Hedin</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7337-2025 artfynd.xlsx
+++ b/artfynd/A 7337-2025 artfynd.xlsx
@@ -1607,7 +1607,7 @@
         <v>134057898</v>
       </c>
       <c r="B10" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>134057882</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>134057894</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>134057897</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>134057893</v>
       </c>
       <c r="B15" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 7337-2025 artfynd.xlsx
+++ b/artfynd/A 7337-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81745487</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387115.1924713838</v>
+        <v>387115</v>
       </c>
       <c r="R2" t="n">
-        <v>6652821.937374118</v>
+        <v>6652822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81745527</v>
+        <v>134057898</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bickberg, Vrm</t>
+          <t>Björnhöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387170.1249846865</v>
+        <v>387114</v>
       </c>
       <c r="R3" t="n">
-        <v>6652994.952014731</v>
+        <v>6652815</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,31 +866,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81745545</v>
+        <v>81745477</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -948,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387153.1419860394</v>
+        <v>386721</v>
       </c>
       <c r="R4" t="n">
-        <v>6652816.771638409</v>
+        <v>6652826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +946,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,53 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81745489</v>
+        <v>81745527</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387115.1924713838</v>
+        <v>387170</v>
       </c>
       <c r="R5" t="n">
-        <v>6652821.937374118</v>
+        <v>6652995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,33 +1043,17 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,19 +1072,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81745477</v>
+        <v>81745534</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1181,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386721.2035205372</v>
+        <v>387149</v>
       </c>
       <c r="R6" t="n">
-        <v>6652826.006363243</v>
+        <v>6652820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,19 +1140,9 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,53 +1169,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81745466</v>
+        <v>81745545</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386868.1916462621</v>
+        <v>387153</v>
       </c>
       <c r="R7" t="n">
-        <v>6653008.204831007</v>
+        <v>6652817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,33 +1237,17 @@
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-10-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1374,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81745534</v>
+        <v>134057894</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,37 +1277,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bickberg, Vrm</t>
+          <t>Björnhöjden, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387149.2262112396</v>
+        <v>386950</v>
       </c>
       <c r="R8" t="n">
-        <v>6652819.894864445</v>
+        <v>6652971</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,22 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,78 +1351,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121172398</v>
+        <v>134057893</v>
       </c>
       <c r="B9" t="n">
-        <v>56567</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bickberg, Vrm</t>
+          <t>Björnhöjden, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386869</v>
+        <v>386795</v>
       </c>
       <c r="R9" t="n">
-        <v>6653009</v>
+        <v>6653020</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1572,12 +1428,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1448,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Hedin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Hedin</t>
+          <t>Max Ljungkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134057898</v>
+        <v>134057897</v>
       </c>
       <c r="B10" t="n">
-        <v>80482</v>
+        <v>79992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1639,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387114</v>
+        <v>387130</v>
       </c>
       <c r="R10" t="n">
-        <v>6652815</v>
+        <v>6652929</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1701,10 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134057882</v>
+        <v>81745466</v>
       </c>
       <c r="B11" t="n">
-        <v>80481</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,19 +1586,22 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnhöjden, Vrm</t>
+          <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>386868</v>
       </c>
       <c r="R11" t="n">
-        <v>6653002</v>
+        <v>6653008</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,17 +1625,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På björklåga.</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,28 +1644,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134057894</v>
+        <v>121172387</v>
       </c>
       <c r="B12" t="n">
-        <v>79123</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,34 +1674,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnhöjden, Vrm</t>
+          <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386950</v>
+        <v>386869</v>
       </c>
       <c r="R12" t="n">
-        <v>6652971</v>
+        <v>6653009</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,12 +1731,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På liggande björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,28 +1750,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Hedin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Hedin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134057897</v>
+        <v>134057882</v>
       </c>
       <c r="B13" t="n">
-        <v>79985</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387130</v>
+        <v>386868</v>
       </c>
       <c r="R13" t="n">
-        <v>6652929</v>
+        <v>6653002</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,6 +1840,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På björklåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134057881</v>
+        <v>81745489</v>
       </c>
       <c r="B14" t="n">
-        <v>8449</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,37 +1882,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnhöjden, Vrm</t>
+          <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386869</v>
+        <v>387115</v>
       </c>
       <c r="R14" t="n">
-        <v>6653002</v>
+        <v>6652822</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,17 +1939,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På fallen murken björkstam där det även växer lunglav</t>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,28 +1958,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134057893</v>
+        <v>127483209</v>
       </c>
       <c r="B15" t="n">
-        <v>79985</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,37 +1988,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnhöjden, Vrm</t>
+          <t>Bickbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386795</v>
+        <v>386655</v>
       </c>
       <c r="R15" t="n">
-        <v>6653020</v>
+        <v>6653062</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,12 +2050,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,22 +2080,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Hedin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Max Ljungkvist</t>
+          <t>Jan Hedin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134057895</v>
+        <v>121172398</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,17 +2120,33 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björnhöjden, Vrm</t>
+          <t>Bickberg, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386989</v>
+        <v>386869</v>
       </c>
       <c r="R16" t="n">
-        <v>6652960</v>
+        <v>6653009</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2261,17 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,15 +2193,515 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Jan Hedin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Hedin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134057892</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>386660</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6652932</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Max Ljungkvist</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Max Ljungkvist</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134057895</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>386989</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6652960</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134057881</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>386869</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6653002</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På fallen murken björkstam där det även växer lunglav</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134057883</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>386946</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6652809</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134057900</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387125</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6653009</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
